--- a/planning-documents/lisbon-trip-budget-dev.xlsx
+++ b/planning-documents/lisbon-trip-budget-dev.xlsx
@@ -22,14 +22,38 @@
     <comment ref="B5" authorId="0">
       <text>
         <r>
-          <t>old screenshot said 830.40. fare changed when maya waited.</t>
+          <t>old price. Maya had a different screenshot.</t>
         </r>
       </text>
     </comment>
-    <comment ref="B11" authorId="0">
+    <comment ref="E8" authorId="0">
       <text>
         <r>
-          <t>why is this wrong. TBD is breaking something obviously.</t>
+          <t>sent me 20 already? i think?</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D10" authorId="0">
+      <text>
+        <r>
+          <t>why is this wrong</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments3.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Author</author>
+  </authors>
+  <commentList>
+    <comment ref="D5" authorId="0">
+      <text>
+        <r>
+          <t>please reply.</t>
         </r>
       </text>
     </comment>
@@ -38,7 +62,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="46">
   <si>
     <t>thing</t>
   </si>
@@ -55,66 +79,60 @@
     <t>notes</t>
   </si>
   <si>
-    <t>chave - Ribeira Riverside (6 x 110)</t>
-  </si>
-  <si>
-    <t>paid ✅</t>
-  </si>
-  <si>
-    <t>chave cleaning fee</t>
-  </si>
-  <si>
-    <t>why isnt this in price</t>
-  </si>
-  <si>
-    <t>chave service fee</t>
-  </si>
-  <si>
-    <t>annoying but ok</t>
-  </si>
-  <si>
-    <t>linha clara air x4</t>
-  </si>
-  <si>
-    <t>fare went up €6.40</t>
-  </si>
-  <si>
-    <t>bags (4)</t>
-  </si>
-  <si>
-    <t>sam has a bag??</t>
+    <t>chave / Ribeira Riverside (6 x 110)</t>
+  </si>
+  <si>
+    <t>paid ✓</t>
+  </si>
+  <si>
+    <t>chave cleaning</t>
+  </si>
+  <si>
+    <t>fee</t>
+  </si>
+  <si>
+    <t>chave service thing</t>
+  </si>
+  <si>
+    <t>yeah</t>
+  </si>
+  <si>
+    <t>linha clara x4</t>
+  </si>
+  <si>
+    <t>paid</t>
+  </si>
+  <si>
+    <t>bags x4</t>
+  </si>
+  <si>
+    <t>sam?</t>
   </si>
   <si>
     <t>rota curta sintra x3</t>
   </si>
   <si>
-    <t>sam no response</t>
-  </si>
-  <si>
-    <t>mare baixa first dinner est</t>
+    <t>mare baixa est</t>
   </si>
   <si>
     <t>priya pay me back</t>
   </si>
   <si>
-    <t>airport shared shuttle</t>
-  </si>
-  <si>
-    <t>tram / metro / random</t>
+    <t>shared airport</t>
+  </si>
+  <si>
+    <t>metro/random</t>
   </si>
   <si>
     <t>TBD</t>
   </si>
   <si>
-    <t>sam fill this in</t>
+    <t/>
   </si>
   <si>
     <t>TOTAL</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
     <t>why is this wrong</t>
   </si>
   <si>
@@ -124,25 +142,22 @@
     <t>paid so far</t>
   </si>
   <si>
-    <t>share estimate</t>
+    <t>share-ish</t>
   </si>
   <si>
     <t>owes dev</t>
   </si>
   <si>
-    <t>status</t>
-  </si>
-  <si>
     <t>Maya</t>
   </si>
   <si>
-    <t>reminded 2x</t>
+    <t>will do it</t>
   </si>
   <si>
     <t>Dev</t>
   </si>
   <si>
-    <t>i am the bank apparently</t>
+    <t>i am not a bank</t>
   </si>
   <si>
     <t>Priya</t>
@@ -157,31 +172,25 @@
     <t>who</t>
   </si>
   <si>
-    <t>outbound</t>
-  </si>
-  <si>
-    <t>return</t>
+    <t>out</t>
+  </si>
+  <si>
+    <t>back</t>
   </si>
   <si>
     <t>bag</t>
   </si>
   <si>
-    <t>paid</t>
-  </si>
-  <si>
     <t>Maya Patel</t>
   </si>
   <si>
-    <t>LC 482 · Thu 20 May · LCY 09:15 → LIS 12:00</t>
-  </si>
-  <si>
-    <t>LC 483 · Wed 26 May · LIS 16:40 → LCY 19:20</t>
-  </si>
-  <si>
-    <t>1 cabin + 1 checked</t>
-  </si>
-  <si>
-    <t>yes</t>
+    <t>LC 482 Thu 20 May LCY 09:15 &gt; LIS 12:00</t>
+  </si>
+  <si>
+    <t>LC 483 Wed 26 May LIS 16:40 &gt; LCY 19:20</t>
+  </si>
+  <si>
+    <t>1 checked</t>
   </si>
   <si>
     <t>Dev Shah</t>
@@ -191,9 +200,6 @@
   </si>
   <si>
     <t>Sam Ferreira</t>
-  </si>
-  <si>
-    <t>sam says TBD</t>
   </si>
 </sst>
 </file>
@@ -203,7 +209,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="€#,##0.00"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -213,9 +219,14 @@
     </font>
     <font>
       <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <name val="Arial"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -224,12 +235,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="D9EAD3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFF2CC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="D9EAD3"/>
+        <fgColor rgb="CFE2F3"/>
       </patternFill>
     </fill>
     <fill>
@@ -250,16 +266,17 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -600,12 +617,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E11"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55" defaultColWidth="11"/>
   <cols>
-    <col min="1" max="1" width="29" customWidth="1"/>
-    <col min="2" max="2" width="13" customWidth="1"/>
+    <col min="1" max="1" width="34" customWidth="1"/>
+    <col min="2" max="2" width="12" customWidth="1"/>
     <col min="4" max="4" width="14" customWidth="1"/>
-    <col min="5" max="5" width="12" customWidth="1"/>
+    <col min="5" max="5" width="10" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -625,20 +642,20 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="3">
+      <c r="B2" s="2">
         <v>660</v>
       </c>
-      <c r="C2" s="2">
+      <c r="C2">
         <v>4</v>
       </c>
-      <c r="D2" s="3">
+      <c r="D2" s="2">
         <f>B2/C2</f>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" t="s">
         <v>6</v>
       </c>
     </row>
@@ -646,13 +663,13 @@
       <c r="A3" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="4">
+      <c r="B3" s="2">
         <v>42.6</v>
       </c>
       <c r="C3">
         <v>4</v>
       </c>
-      <c r="D3" s="4">
+      <c r="D3" s="2">
         <f>B3/C3</f>
       </c>
       <c r="E3" t="s">
@@ -663,33 +680,33 @@
       <c r="A4" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="4">
+      <c r="B4" s="2">
         <v>31.8</v>
       </c>
       <c r="C4">
         <v>4</v>
       </c>
-      <c r="D4" s="4">
+      <c r="D4" s="2">
         <f>B4/C4</f>
       </c>
       <c r="E4" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+    <row r="5" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="3" t="s">
         <v>11</v>
       </c>
       <c r="B5" s="4">
-        <v>849.6</v>
-      </c>
-      <c r="C5">
+        <v>830.4</v>
+      </c>
+      <c r="C5" s="3">
         <v>4</v>
       </c>
       <c r="D5" s="4">
         <f>B5/C5</f>
       </c>
-      <c r="E5" t="s">
+      <c r="E5" s="3" t="s">
         <v>12</v>
       </c>
     </row>
@@ -697,13 +714,13 @@
       <c r="A6" t="s">
         <v>13</v>
       </c>
-      <c r="B6" s="4">
+      <c r="B6" s="2">
         <v>108</v>
       </c>
       <c r="C6">
         <v>4</v>
       </c>
-      <c r="D6" s="4">
+      <c r="D6" s="2">
         <f>B6/C6</f>
       </c>
       <c r="E6" t="s">
@@ -723,76 +740,77 @@
       <c r="D7" s="6">
         <f>B7/C7</f>
       </c>
-      <c r="E7" s="7" t="s">
-        <v>16</v>
+      <c r="E7" s="5" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>17</v>
-      </c>
-      <c r="B8" s="4">
+        <v>16</v>
+      </c>
+      <c r="B8" s="2">
         <v>177.2</v>
       </c>
       <c r="C8">
         <v>4</v>
       </c>
-      <c r="D8" s="4">
+      <c r="D8" s="2">
         <f>B8/C8</f>
       </c>
       <c r="E8" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>19</v>
-      </c>
-      <c r="B9" s="4">
+        <v>18</v>
+      </c>
+      <c r="B9" s="2">
         <v>48</v>
       </c>
       <c r="C9">
         <v>4</v>
       </c>
-      <c r="D9" s="4">
+      <c r="D9" s="2">
         <f>B9/C9</f>
       </c>
       <c r="E9" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
+        <v>19</v>
+      </c>
+      <c r="B10" s="2" t="s">
         <v>20</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>21</v>
       </c>
       <c r="C10">
         <v>4</v>
       </c>
-      <c r="D10" s="4">
+      <c r="D10" s="2" t="str">
         <f>B10/C10</f>
+        <v>#VALUE!</v>
       </c>
       <c r="E10" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
+        <v>22</v>
+      </c>
+      <c r="B11" s="2">
+        <f>SUM(B2:B10)</f>
+      </c>
+      <c r="C11" t="s">
+        <v>21</v>
+      </c>
+      <c r="D11" s="2">
+        <f>D2+D3+D4+D5+D6+D7+D8+D9+D10</f>
+      </c>
+      <c r="E11" t="s">
         <v>23</v>
-      </c>
-      <c r="B11" s="4">
-        <f>SUM(B2:B10)</f>
-      </c>
-      <c r="C11" t="s">
-        <v>24</v>
-      </c>
-      <c r="D11" s="4">
-        <f>SUM(D2:D10)</f>
-      </c>
-      <c r="E11" t="s">
-        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -805,35 +823,33 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E5"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55" defaultColWidth="12"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
-    <col min="2" max="2" width="16" customWidth="1"/>
-    <col min="3" max="3" width="17" customWidth="1"/>
-    <col min="4" max="4" width="15" customWidth="1"/>
-    <col min="5" max="5" width="22" customWidth="1"/>
+    <col min="2" max="4" width="13" customWidth="1"/>
+    <col min="5" max="5" width="28" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:5" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C1" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="D1" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>30</v>
+      <c r="E1" s="7" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -845,12 +861,12 @@
         <f>C2-B2</f>
       </c>
       <c r="E2" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="B3">
         <v>2014</v>
@@ -862,15 +878,15 @@
         <f>C3-B3</f>
       </c>
       <c r="E3" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="B4">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="C4">
         <f>budget!D11</f>
@@ -879,12 +895,12 @@
         <f>C4-B4</f>
       </c>
       <c r="E4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -896,7 +912,7 @@
         <f>C5-B5</f>
       </c>
       <c r="E5" s="8" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -907,103 +923,88 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E5"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <dimension ref="A1:D5"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55" defaultColWidth="13"/>
   <cols>
-    <col min="1" max="1" width="19" customWidth="1"/>
-    <col min="2" max="3" width="35" customWidth="1"/>
-    <col min="4" max="4" width="18" customWidth="1"/>
-    <col min="5" max="5" width="14" customWidth="1"/>
+    <col min="1" max="1" width="18" customWidth="1"/>
+    <col min="2" max="3" width="36" customWidth="1"/>
+    <col min="4" max="4" width="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:4" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="B1" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="D1" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="B1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>39</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="B2" t="s">
         <v>40</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="C2" t="s">
         <v>41</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="D2" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
         <v>43</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B3" t="s">
+        <v>40</v>
+      </c>
+      <c r="C3" t="s">
+        <v>41</v>
+      </c>
+      <c r="D3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
         <v>44</v>
       </c>
-      <c r="C2" t="s">
+      <c r="B4" t="s">
+        <v>40</v>
+      </c>
+      <c r="C4" t="s">
+        <v>41</v>
+      </c>
+      <c r="D4" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
         <v>45</v>
       </c>
-      <c r="D2" t="s">
-        <v>46</v>
-      </c>
-      <c r="E2" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>48</v>
-      </c>
-      <c r="B3" t="s">
-        <v>44</v>
-      </c>
-      <c r="C3" t="s">
-        <v>45</v>
-      </c>
-      <c r="D3" t="s">
-        <v>46</v>
-      </c>
-      <c r="E3" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>49</v>
-      </c>
-      <c r="B4" t="s">
-        <v>44</v>
-      </c>
-      <c r="C4" t="s">
-        <v>45</v>
-      </c>
-      <c r="D4" t="s">
-        <v>46</v>
-      </c>
-      <c r="E4" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>50</v>
-      </c>
       <c r="B5" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="C5" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="D5" t="s">
-        <v>51</v>
-      </c>
-      <c r="E5" t="s">
-        <v>47</v>
+        <v>20</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 
